--- a/SALE TRABAJO LARGO.xlsx
+++ b/SALE TRABAJO LARGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\TRABAJO FINAL MATERIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B526BEB7-8C51-40D9-8141-447726C6ACA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED41EC29-B299-4CFC-8067-EABA92DDBA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0FCE4E4-E062-49E2-A859-ABF82E26F938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C0FCE4E4-E062-49E2-A859-ABF82E26F938}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS EPORTABLES" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="211">
   <si>
     <t>ID</t>
   </si>
@@ -667,67 +667,10 @@
     <t>SKU</t>
   </si>
   <si>
-    <t>Jan-20</t>
+    <t>ß=</t>
   </si>
   <si>
-    <t>Apr-20</t>
-  </si>
-  <si>
-    <t>Aug-20</t>
-  </si>
-  <si>
-    <t>Dec-20</t>
-  </si>
-  <si>
-    <t>Jan-21</t>
-  </si>
-  <si>
-    <t>Apr-21</t>
-  </si>
-  <si>
-    <t>Aug-21</t>
-  </si>
-  <si>
-    <t>Dec-21</t>
-  </si>
-  <si>
-    <t>Jan-22</t>
-  </si>
-  <si>
-    <t>Apr-22</t>
-  </si>
-  <si>
-    <t>Aug-22</t>
-  </si>
-  <si>
-    <t>Dec-22</t>
-  </si>
-  <si>
-    <t>Jan-23</t>
-  </si>
-  <si>
-    <t>Apr-23</t>
-  </si>
-  <si>
-    <t>Aug-23</t>
-  </si>
-  <si>
-    <t>Dec-23</t>
-  </si>
-  <si>
-    <t>Jan-24</t>
-  </si>
-  <si>
-    <t>Apr-24</t>
-  </si>
-  <si>
-    <t>Aug-24</t>
-  </si>
-  <si>
-    <t>Dec-24</t>
-  </si>
-  <si>
-    <t>Jan-25</t>
+    <t>ß1=</t>
   </si>
 </sst>
 </file>
@@ -788,6 +731,1291 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-EC"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja3!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SKU1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.9929125749085688E-2"/>
+                  <c:y val="-0.53492661602118219"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-EC"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>Hoja3!$B$1:$BJ$1</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yy</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>43831</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43862</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43891</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43952</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43983</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44044</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44075</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44105</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44136</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44166</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44197</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44228</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44256</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>44287</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>44317</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44348</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44378</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44409</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44440</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44470</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44501</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44531</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44562</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44593</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44621</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44652</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44682</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44713</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44743</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44774</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44805</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44835</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44866</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44896</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>44927</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>44958</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44986</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45017</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>45047</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>45078</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>45108</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45139</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45170</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45200</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>45231</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>45261</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>45292</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>45323</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>45352</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>45383</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>45413</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>45444</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>45474</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>45505</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>45536</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>45627</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>45658</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja3!$B$2:$BJ$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>307</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>334</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>347</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>154</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0866-4F68-8839-3B2F56E2A022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="619205264"/>
+        <c:axId val="619205744"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="619205264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mmm\-yy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="619205744"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="619205744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-EC"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="619205264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-EC"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>754380</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BF973EB-2868-E0EB-F8DA-62EE2C8D44C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4587,8 +5815,8 @@
       <c r="A1" t="s">
         <v>208</v>
       </c>
-      <c r="B1" t="s">
-        <v>209</v>
+      <c r="B1" s="3">
+        <v>43831</v>
       </c>
       <c r="C1" s="3">
         <v>43862</v>
@@ -4596,8 +5824,8 @@
       <c r="D1" s="3">
         <v>43891</v>
       </c>
-      <c r="E1" t="s">
-        <v>210</v>
+      <c r="E1" s="3">
+        <v>43922</v>
       </c>
       <c r="F1" s="3">
         <v>43952</v>
@@ -4608,8 +5836,8 @@
       <c r="H1" s="3">
         <v>44013</v>
       </c>
-      <c r="I1" t="s">
-        <v>211</v>
+      <c r="I1" s="3">
+        <v>44044</v>
       </c>
       <c r="J1" s="3">
         <v>44075</v>
@@ -4620,11 +5848,11 @@
       <c r="L1" s="3">
         <v>44136</v>
       </c>
-      <c r="M1" t="s">
-        <v>212</v>
-      </c>
-      <c r="N1" t="s">
-        <v>213</v>
+      <c r="M1" s="3">
+        <v>44166</v>
+      </c>
+      <c r="N1" s="3">
+        <v>44197</v>
       </c>
       <c r="O1" s="3">
         <v>44228</v>
@@ -4632,8 +5860,8 @@
       <c r="P1" s="3">
         <v>44256</v>
       </c>
-      <c r="Q1" t="s">
-        <v>214</v>
+      <c r="Q1" s="3">
+        <v>44287</v>
       </c>
       <c r="R1" s="3">
         <v>44317</v>
@@ -4644,8 +5872,8 @@
       <c r="T1" s="3">
         <v>44378</v>
       </c>
-      <c r="U1" t="s">
-        <v>215</v>
+      <c r="U1" s="3">
+        <v>44409</v>
       </c>
       <c r="V1" s="3">
         <v>44440</v>
@@ -4656,11 +5884,11 @@
       <c r="X1" s="3">
         <v>44501</v>
       </c>
-      <c r="Y1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>217</v>
+      <c r="Y1" s="3">
+        <v>44531</v>
+      </c>
+      <c r="Z1" s="3">
+        <v>44562</v>
       </c>
       <c r="AA1" s="3">
         <v>44593</v>
@@ -4668,8 +5896,8 @@
       <c r="AB1" s="3">
         <v>44621</v>
       </c>
-      <c r="AC1" t="s">
-        <v>218</v>
+      <c r="AC1" s="3">
+        <v>44652</v>
       </c>
       <c r="AD1" s="3">
         <v>44682</v>
@@ -4680,8 +5908,8 @@
       <c r="AF1" s="3">
         <v>44743</v>
       </c>
-      <c r="AG1" t="s">
-        <v>219</v>
+      <c r="AG1" s="3">
+        <v>44774</v>
       </c>
       <c r="AH1" s="3">
         <v>44805</v>
@@ -4692,11 +5920,11 @@
       <c r="AJ1" s="3">
         <v>44866</v>
       </c>
-      <c r="AK1" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>221</v>
+      <c r="AK1" s="3">
+        <v>44896</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>44927</v>
       </c>
       <c r="AM1" s="3">
         <v>44958</v>
@@ -4704,8 +5932,8 @@
       <c r="AN1" s="3">
         <v>44986</v>
       </c>
-      <c r="AO1" t="s">
-        <v>222</v>
+      <c r="AO1" s="3">
+        <v>45017</v>
       </c>
       <c r="AP1" s="3">
         <v>45047</v>
@@ -4716,8 +5944,8 @@
       <c r="AR1" s="3">
         <v>45108</v>
       </c>
-      <c r="AS1" t="s">
-        <v>223</v>
+      <c r="AS1" s="3">
+        <v>45139</v>
       </c>
       <c r="AT1" s="3">
         <v>45170</v>
@@ -4728,11 +5956,11 @@
       <c r="AV1" s="3">
         <v>45231</v>
       </c>
-      <c r="AW1" t="s">
-        <v>224</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>225</v>
+      <c r="AW1" s="3">
+        <v>45261</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>45292</v>
       </c>
       <c r="AY1" s="3">
         <v>45323</v>
@@ -4740,8 +5968,8 @@
       <c r="AZ1" s="3">
         <v>45352</v>
       </c>
-      <c r="BA1" t="s">
-        <v>226</v>
+      <c r="BA1" s="3">
+        <v>45383</v>
       </c>
       <c r="BB1" s="3">
         <v>45413</v>
@@ -4752,8 +5980,8 @@
       <c r="BD1" s="3">
         <v>45474</v>
       </c>
-      <c r="BE1" t="s">
-        <v>227</v>
+      <c r="BE1" s="3">
+        <v>45505</v>
       </c>
       <c r="BF1" s="3">
         <v>45536</v>
@@ -4764,11 +5992,11 @@
       <c r="BH1" s="3">
         <v>45597</v>
       </c>
-      <c r="BI1" t="s">
-        <v>228</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>229</v>
+      <c r="BI1" s="3">
+        <v>45627</v>
+      </c>
+      <c r="BJ1" s="3">
+        <v>45658</v>
       </c>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.3">
@@ -21698,9 +22926,409 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05D5C55-0FE8-43E1-962F-FCC0F6999375}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BK7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C1" s="3">
+        <v>43862</v>
+      </c>
+      <c r="D1" s="3">
+        <v>43891</v>
+      </c>
+      <c r="E1" s="3">
+        <v>43922</v>
+      </c>
+      <c r="F1" s="3">
+        <v>43952</v>
+      </c>
+      <c r="G1" s="3">
+        <v>43983</v>
+      </c>
+      <c r="H1" s="3">
+        <v>44013</v>
+      </c>
+      <c r="I1" s="3">
+        <v>44044</v>
+      </c>
+      <c r="J1" s="3">
+        <v>44075</v>
+      </c>
+      <c r="K1" s="3">
+        <v>44105</v>
+      </c>
+      <c r="L1" s="3">
+        <v>44136</v>
+      </c>
+      <c r="M1" s="3">
+        <v>44166</v>
+      </c>
+      <c r="N1" s="3">
+        <v>44197</v>
+      </c>
+      <c r="O1" s="3">
+        <v>44228</v>
+      </c>
+      <c r="P1" s="3">
+        <v>44256</v>
+      </c>
+      <c r="Q1" s="3">
+        <v>44287</v>
+      </c>
+      <c r="R1" s="3">
+        <v>44317</v>
+      </c>
+      <c r="S1" s="3">
+        <v>44348</v>
+      </c>
+      <c r="T1" s="3">
+        <v>44378</v>
+      </c>
+      <c r="U1" s="3">
+        <v>44409</v>
+      </c>
+      <c r="V1" s="3">
+        <v>44440</v>
+      </c>
+      <c r="W1" s="3">
+        <v>44470</v>
+      </c>
+      <c r="X1" s="3">
+        <v>44501</v>
+      </c>
+      <c r="Y1" s="3">
+        <v>44531</v>
+      </c>
+      <c r="Z1" s="3">
+        <v>44562</v>
+      </c>
+      <c r="AA1" s="3">
+        <v>44593</v>
+      </c>
+      <c r="AB1" s="3">
+        <v>44621</v>
+      </c>
+      <c r="AC1" s="3">
+        <v>44652</v>
+      </c>
+      <c r="AD1" s="3">
+        <v>44682</v>
+      </c>
+      <c r="AE1" s="3">
+        <v>44713</v>
+      </c>
+      <c r="AF1" s="3">
+        <v>44743</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>44774</v>
+      </c>
+      <c r="AH1" s="3">
+        <v>44805</v>
+      </c>
+      <c r="AI1" s="3">
+        <v>44835</v>
+      </c>
+      <c r="AJ1" s="3">
+        <v>44866</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>44896</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>44927</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>44958</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>44986</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>45017</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>45047</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>45078</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>45108</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>45139</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>45170</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>45200</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>45231</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>45261</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>45292</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>45323</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>45352</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>45383</v>
+      </c>
+      <c r="BB1" s="3">
+        <v>45413</v>
+      </c>
+      <c r="BC1" s="3">
+        <v>45444</v>
+      </c>
+      <c r="BD1" s="3">
+        <v>45474</v>
+      </c>
+      <c r="BE1" s="3">
+        <v>45505</v>
+      </c>
+      <c r="BF1" s="3">
+        <v>45536</v>
+      </c>
+      <c r="BG1" s="3">
+        <v>45566</v>
+      </c>
+      <c r="BH1" s="3">
+        <v>45597</v>
+      </c>
+      <c r="BI1" s="3">
+        <v>45627</v>
+      </c>
+      <c r="BJ1" s="3">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>268</v>
+      </c>
+      <c r="C2">
+        <v>301</v>
+      </c>
+      <c r="D2">
+        <v>268</v>
+      </c>
+      <c r="E2">
+        <v>253</v>
+      </c>
+      <c r="F2">
+        <v>161</v>
+      </c>
+      <c r="G2">
+        <v>318</v>
+      </c>
+      <c r="H2">
+        <v>125</v>
+      </c>
+      <c r="I2">
+        <v>87</v>
+      </c>
+      <c r="J2">
+        <v>295</v>
+      </c>
+      <c r="K2">
+        <v>79</v>
+      </c>
+      <c r="L2">
+        <v>64</v>
+      </c>
+      <c r="M2">
+        <v>227</v>
+      </c>
+      <c r="N2">
+        <v>243</v>
+      </c>
+      <c r="O2">
+        <v>325</v>
+      </c>
+      <c r="P2">
+        <v>307</v>
+      </c>
+      <c r="Q2">
+        <v>98</v>
+      </c>
+      <c r="R2">
+        <v>172</v>
+      </c>
+      <c r="S2">
+        <v>108</v>
+      </c>
+      <c r="T2">
+        <v>390</v>
+      </c>
+      <c r="U2">
+        <v>86</v>
+      </c>
+      <c r="V2">
+        <v>293</v>
+      </c>
+      <c r="W2">
+        <v>187</v>
+      </c>
+      <c r="X2">
+        <v>85</v>
+      </c>
+      <c r="Y2">
+        <v>244</v>
+      </c>
+      <c r="Z2">
+        <v>235</v>
+      </c>
+      <c r="AA2">
+        <v>77</v>
+      </c>
+      <c r="AB2">
+        <v>318</v>
+      </c>
+      <c r="AC2">
+        <v>114</v>
+      </c>
+      <c r="AD2">
+        <v>222</v>
+      </c>
+      <c r="AE2">
+        <v>118</v>
+      </c>
+      <c r="AF2">
+        <v>200</v>
+      </c>
+      <c r="AG2">
+        <v>209</v>
+      </c>
+      <c r="AH2">
+        <v>115</v>
+      </c>
+      <c r="AI2">
+        <v>159</v>
+      </c>
+      <c r="AJ2">
+        <v>120</v>
+      </c>
+      <c r="AK2">
+        <v>106</v>
+      </c>
+      <c r="AL2">
+        <v>203</v>
+      </c>
+      <c r="AM2">
+        <v>334</v>
+      </c>
+      <c r="AN2">
+        <v>224</v>
+      </c>
+      <c r="AO2">
+        <v>189</v>
+      </c>
+      <c r="AP2">
+        <v>187</v>
+      </c>
+      <c r="AQ2">
+        <v>163</v>
+      </c>
+      <c r="AR2">
+        <v>64</v>
+      </c>
+      <c r="AS2">
+        <v>274</v>
+      </c>
+      <c r="AT2">
+        <v>249</v>
+      </c>
+      <c r="AU2">
+        <v>56</v>
+      </c>
+      <c r="AV2">
+        <v>139</v>
+      </c>
+      <c r="AW2">
+        <v>87</v>
+      </c>
+      <c r="AX2">
+        <v>347</v>
+      </c>
+      <c r="AY2">
+        <v>257</v>
+      </c>
+      <c r="AZ2">
+        <v>229</v>
+      </c>
+      <c r="BA2">
+        <v>106</v>
+      </c>
+      <c r="BB2">
+        <v>163</v>
+      </c>
+      <c r="BC2">
+        <v>196</v>
+      </c>
+      <c r="BD2">
+        <v>115</v>
+      </c>
+      <c r="BE2">
+        <v>198</v>
+      </c>
+      <c r="BF2">
+        <v>71</v>
+      </c>
+      <c r="BG2">
+        <v>211</v>
+      </c>
+      <c r="BH2">
+        <v>119</v>
+      </c>
+      <c r="BI2">
+        <v>129</v>
+      </c>
+      <c r="BJ2">
+        <v>154</v>
+      </c>
+      <c r="BK2">
+        <f>Q6+BK1*Q7</f>
+        <v>1796.8451661602789</v>
+      </c>
+    </row>
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="P6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q6">
+        <f>INTERCEPT(B2:BJ2,B1:BJ1)</f>
+        <v>1796.8451661602789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="P7" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q7">
+        <f>SLOPE(B2:BJ2,B1:BJ1)</f>
+        <v>-3.5966666056921809E-2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SALE TRABAJO LARGO.xlsx
+++ b/SALE TRABAJO LARGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\TRABAJO FINAL MATERIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED41EC29-B299-4CFC-8067-EABA92DDBA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500A9FAF-9DE2-4125-8254-C6DA94720AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C0FCE4E4-E062-49E2-A859-ABF82E26F938}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0FCE4E4-E062-49E2-A859-ABF82E26F938}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS EPORTABLES" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="216">
   <si>
     <t>ID</t>
   </si>
@@ -672,15 +672,31 @@
   <si>
     <t>ß1=</t>
   </si>
+  <si>
+    <t>ESTACIONALIDAD 1</t>
+  </si>
+  <si>
+    <t>PROMEDIO</t>
+  </si>
+  <si>
+    <t>TENDENCIA</t>
+  </si>
+  <si>
+    <t>ESTACIONALIDAD</t>
+  </si>
+  <si>
+    <t>FORECAST</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]&quot;$&quot;\-#,##0.00"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -688,13 +704,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -706,18 +761,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -747,36 +818,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-EC"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -863,190 +904,190 @@
             <c:numRef>
               <c:f>Hoja3!$B$1:$BJ$1</c:f>
               <c:numCache>
-                <c:formatCode>mmm\-yy</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>43831</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43862</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43891</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43922</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43952</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43983</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44013</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44044</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44075</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>44105</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>44136</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44166</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>44197</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>44228</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>44256</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>44287</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>44317</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44348</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>44378</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44409</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>44440</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>44470</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>44501</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>44531</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>44562</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>44593</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>44621</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>44652</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>44682</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>44713</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>44743</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>44774</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>44805</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>44835</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>44866</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>44896</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>44927</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>44958</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>44986</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>45017</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>45047</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>45078</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>45108</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>45139</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>45170</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>45200</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>45231</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>45261</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>45292</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>45323</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>45352</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>45383</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>45413</c:v>
+                  <c:v>53</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>45444</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>45474</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>45505</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>45536</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>45566</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>45597</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>45627</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>45658</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1055,7 +1096,7 @@
             <c:numRef>
               <c:f>Hoja3!$B$2:$BJ$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>268</c:v>
@@ -1237,7 +1278,7 @@
                 <c:pt idx="59">
                   <c:v>129</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="60" formatCode="General">
                   <c:v>154</c:v>
                 </c:pt>
               </c:numCache>
@@ -1247,6 +1288,223 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-0866-4F68-8839-3B2F56E2A022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>FORECAST</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja3!$B$5:$BJ$5</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="61"/>
+                <c:pt idx="0">
+                  <c:v>306.17665380617797</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>296.7015351223809</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>314.35990244583445</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>175.01083887969997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>211.161592972557</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>205.52037119913197</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>199.27879851012119</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200.70331560843596</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>224.3496858557493</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>156.70202830597188</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>120.40334424805414</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>171.25771733122755</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>287.94491158209888</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>278.94589571732922</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>295.45323901911922</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>164.43207732476174</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>198.33303134056951</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>192.97099333388874</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>187.04830597519253</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>188.32207143561533</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>210.43819818208553</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>146.9347695800567</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>112.85940285944889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>160.47114578457865</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>269.71316935801985</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>261.19025631227748</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>276.546575592404</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>153.85331576982347</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>185.50446970858195</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>180.42161546864554</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>174.81781344026388</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>175.9408272627947</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>196.52671050842176</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>137.16751085414154</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>105.31546147084364</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>149.68457423792975</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>251.4814271339408</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>243.43461690722583</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>257.63991216568877</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>143.27455421488526</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>172.6759080765944</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>167.87223760340231</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>162.58732090533522</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>163.55958308997404</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>182.61522283475799</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>127.40025212822637</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>97.771520082238411</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>138.89800269128091</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>233.24968490986171</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>225.67897750217415</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>238.73324873897354</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>132.69579265994699</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>159.84734644460684</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>155.32285973815911</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>150.35682837040662</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>151.17833891715338</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>168.70373516109419</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>117.63299340231119</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>90.227578693633149</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>128.11143114463201</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>215.01794268578266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0866-4F68-8839-3B2F56E2A022}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1263,14 +1521,14 @@
         <c:axId val="619205264"/>
         <c:axId val="619205744"/>
       </c:lineChart>
-      <c:dateAx>
+      <c:catAx>
         <c:axId val="619205264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mmm\-yy" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1310,9 +1568,10 @@
         <c:crossAx val="619205744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="months"/>
-      </c:dateAx>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="619205744"/>
         <c:scaling>
@@ -1334,7 +1593,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1983,13 +2242,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>487680</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>125730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>754380</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -22926,408 +23185,1895 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05D5C55-0FE8-43E1-962F-FCC0F6999375}">
-  <dimension ref="A1:BK7"/>
+  <dimension ref="A1:BK22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:63" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C1" s="3">
-        <v>43862</v>
-      </c>
-      <c r="D1" s="3">
-        <v>43891</v>
-      </c>
-      <c r="E1" s="3">
-        <v>43922</v>
-      </c>
-      <c r="F1" s="3">
-        <v>43952</v>
-      </c>
-      <c r="G1" s="3">
-        <v>43983</v>
-      </c>
-      <c r="H1" s="3">
-        <v>44013</v>
-      </c>
-      <c r="I1" s="3">
-        <v>44044</v>
-      </c>
-      <c r="J1" s="3">
-        <v>44075</v>
-      </c>
-      <c r="K1" s="3">
-        <v>44105</v>
-      </c>
-      <c r="L1" s="3">
-        <v>44136</v>
-      </c>
-      <c r="M1" s="3">
-        <v>44166</v>
-      </c>
-      <c r="N1" s="3">
-        <v>44197</v>
-      </c>
-      <c r="O1" s="3">
-        <v>44228</v>
-      </c>
-      <c r="P1" s="3">
-        <v>44256</v>
-      </c>
-      <c r="Q1" s="3">
-        <v>44287</v>
-      </c>
-      <c r="R1" s="3">
-        <v>44317</v>
-      </c>
-      <c r="S1" s="3">
-        <v>44348</v>
-      </c>
-      <c r="T1" s="3">
-        <v>44378</v>
-      </c>
-      <c r="U1" s="3">
-        <v>44409</v>
-      </c>
-      <c r="V1" s="3">
-        <v>44440</v>
-      </c>
-      <c r="W1" s="3">
-        <v>44470</v>
-      </c>
-      <c r="X1" s="3">
-        <v>44501</v>
-      </c>
-      <c r="Y1" s="3">
-        <v>44531</v>
-      </c>
-      <c r="Z1" s="3">
-        <v>44562</v>
-      </c>
-      <c r="AA1" s="3">
-        <v>44593</v>
-      </c>
-      <c r="AB1" s="3">
-        <v>44621</v>
-      </c>
-      <c r="AC1" s="3">
-        <v>44652</v>
-      </c>
-      <c r="AD1" s="3">
-        <v>44682</v>
-      </c>
-      <c r="AE1" s="3">
-        <v>44713</v>
-      </c>
-      <c r="AF1" s="3">
-        <v>44743</v>
-      </c>
-      <c r="AG1" s="3">
-        <v>44774</v>
-      </c>
-      <c r="AH1" s="3">
-        <v>44805</v>
-      </c>
-      <c r="AI1" s="3">
-        <v>44835</v>
-      </c>
-      <c r="AJ1" s="3">
-        <v>44866</v>
-      </c>
-      <c r="AK1" s="3">
-        <v>44896</v>
-      </c>
-      <c r="AL1" s="3">
-        <v>44927</v>
-      </c>
-      <c r="AM1" s="3">
-        <v>44958</v>
-      </c>
-      <c r="AN1" s="3">
-        <v>44986</v>
-      </c>
-      <c r="AO1" s="3">
-        <v>45017</v>
-      </c>
-      <c r="AP1" s="3">
-        <v>45047</v>
-      </c>
-      <c r="AQ1" s="3">
-        <v>45078</v>
-      </c>
-      <c r="AR1" s="3">
-        <v>45108</v>
-      </c>
-      <c r="AS1" s="3">
-        <v>45139</v>
-      </c>
-      <c r="AT1" s="3">
-        <v>45170</v>
-      </c>
-      <c r="AU1" s="3">
-        <v>45200</v>
-      </c>
-      <c r="AV1" s="3">
-        <v>45231</v>
-      </c>
-      <c r="AW1" s="3">
-        <v>45261</v>
-      </c>
-      <c r="AX1" s="3">
-        <v>45292</v>
-      </c>
-      <c r="AY1" s="3">
-        <v>45323</v>
-      </c>
-      <c r="AZ1" s="3">
-        <v>45352</v>
-      </c>
-      <c r="BA1" s="3">
-        <v>45383</v>
-      </c>
-      <c r="BB1" s="3">
-        <v>45413</v>
-      </c>
-      <c r="BC1" s="3">
-        <v>45444</v>
-      </c>
-      <c r="BD1" s="3">
-        <v>45474</v>
-      </c>
-      <c r="BE1" s="3">
-        <v>45505</v>
-      </c>
-      <c r="BF1" s="3">
-        <v>45536</v>
-      </c>
-      <c r="BG1" s="3">
-        <v>45566</v>
-      </c>
-      <c r="BH1" s="3">
-        <v>45597</v>
-      </c>
-      <c r="BI1" s="3">
-        <v>45627</v>
-      </c>
-      <c r="BJ1" s="3">
-        <v>45658</v>
+      <c r="B1" s="10">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10">
+        <v>9</v>
+      </c>
+      <c r="K1" s="10">
+        <v>10</v>
+      </c>
+      <c r="L1" s="10">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10">
+        <v>12</v>
+      </c>
+      <c r="N1" s="10">
+        <v>13</v>
+      </c>
+      <c r="O1" s="10">
+        <v>14</v>
+      </c>
+      <c r="P1" s="10">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="10">
+        <v>16</v>
+      </c>
+      <c r="R1" s="10">
+        <v>17</v>
+      </c>
+      <c r="S1" s="10">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10">
+        <v>19</v>
+      </c>
+      <c r="U1" s="10">
+        <v>20</v>
+      </c>
+      <c r="V1" s="10">
+        <v>21</v>
+      </c>
+      <c r="W1" s="10">
+        <v>22</v>
+      </c>
+      <c r="X1" s="10">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="10">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="10">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="10">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="10">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="10">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="10">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="10">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="10">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="10">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="10">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="10">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="10">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="10">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="10">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="10">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="10">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="10">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="10">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="10">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="10">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="10">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="10">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="10">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="10">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="10">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="10">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="10">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="10">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="10">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="10">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="10">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="10">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="10">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="10">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="10">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="10">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="10">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="10">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="10">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>268</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>301</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>268</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>253</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>161</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>318</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>125</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="4">
         <v>87</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="4">
         <v>295</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="4">
         <v>79</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="4">
         <v>64</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="4">
         <v>227</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="4">
         <v>243</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="4">
         <v>325</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="4">
         <v>307</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="4">
         <v>98</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="4">
         <v>172</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="4">
         <v>108</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="4">
         <v>390</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="4">
         <v>86</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="4">
         <v>293</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="4">
         <v>187</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="4">
         <v>85</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="4">
         <v>244</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="4">
         <v>235</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="4">
         <v>77</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="4">
         <v>318</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="4">
         <v>114</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="4">
         <v>222</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="4">
         <v>118</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="4">
         <v>200</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="4">
         <v>209</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="4">
         <v>115</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="4">
         <v>159</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="4">
         <v>120</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="4">
         <v>106</v>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="4">
         <v>203</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="4">
         <v>334</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="4">
         <v>224</v>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="4">
         <v>189</v>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="4">
         <v>187</v>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" s="4">
         <v>163</v>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="4">
         <v>64</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="4">
         <v>274</v>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="4">
         <v>249</v>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="4">
         <v>56</v>
       </c>
-      <c r="AV2">
+      <c r="AV2" s="4">
         <v>139</v>
       </c>
-      <c r="AW2">
+      <c r="AW2" s="4">
         <v>87</v>
       </c>
-      <c r="AX2">
+      <c r="AX2" s="4">
         <v>347</v>
       </c>
-      <c r="AY2">
+      <c r="AY2" s="4">
         <v>257</v>
       </c>
-      <c r="AZ2">
+      <c r="AZ2" s="4">
         <v>229</v>
       </c>
-      <c r="BA2">
+      <c r="BA2" s="4">
         <v>106</v>
       </c>
-      <c r="BB2">
+      <c r="BB2" s="4">
         <v>163</v>
       </c>
-      <c r="BC2">
+      <c r="BC2" s="4">
         <v>196</v>
       </c>
-      <c r="BD2">
+      <c r="BD2" s="4">
         <v>115</v>
       </c>
-      <c r="BE2">
+      <c r="BE2" s="4">
         <v>198</v>
       </c>
-      <c r="BF2">
+      <c r="BF2" s="4">
         <v>71</v>
       </c>
-      <c r="BG2">
+      <c r="BG2" s="4">
         <v>211</v>
       </c>
-      <c r="BH2">
+      <c r="BH2" s="4">
         <v>119</v>
       </c>
-      <c r="BI2">
+      <c r="BI2" s="4">
         <v>129</v>
       </c>
-      <c r="BJ2">
+      <c r="BJ2" s="8">
         <v>154</v>
       </c>
-      <c r="BK2">
-        <f>Q6+BK1*Q7</f>
-        <v>1796.8451661602789</v>
-      </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="P6" t="s">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="15">
+        <f t="shared" ref="B3:BJ3" si="0">$Q$9+B1*$Q$10</f>
+        <v>220.37650273224043</v>
+      </c>
+      <c r="C3" s="15">
+        <f t="shared" si="0"/>
+        <v>219.28294896730574</v>
+      </c>
+      <c r="D3" s="15">
+        <f t="shared" si="0"/>
+        <v>218.18939520237103</v>
+      </c>
+      <c r="E3" s="15">
+        <f t="shared" si="0"/>
+        <v>217.09584143743632</v>
+      </c>
+      <c r="F3" s="15">
+        <f t="shared" si="0"/>
+        <v>216.00228767250161</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" si="0"/>
+        <v>214.90873390756693</v>
+      </c>
+      <c r="H3" s="15">
+        <f t="shared" si="0"/>
+        <v>213.81518014263222</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" si="0"/>
+        <v>212.7216263776975</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" si="0"/>
+        <v>211.62807261276279</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" si="0"/>
+        <v>210.53451884782811</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" si="0"/>
+        <v>209.4409650828934</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" si="0"/>
+        <v>208.34741131795869</v>
+      </c>
+      <c r="N3" s="15">
+        <f t="shared" si="0"/>
+        <v>207.25385755302398</v>
+      </c>
+      <c r="O3" s="15">
+        <f t="shared" si="0"/>
+        <v>206.16030378808929</v>
+      </c>
+      <c r="P3" s="15">
+        <f t="shared" si="0"/>
+        <v>205.06675002315458</v>
+      </c>
+      <c r="Q3" s="15">
+        <f t="shared" si="0"/>
+        <v>203.97319625821987</v>
+      </c>
+      <c r="R3" s="15">
+        <f t="shared" si="0"/>
+        <v>202.87964249328519</v>
+      </c>
+      <c r="S3" s="15">
+        <f t="shared" si="0"/>
+        <v>201.78608872835048</v>
+      </c>
+      <c r="T3" s="15">
+        <f t="shared" si="0"/>
+        <v>200.69253496341577</v>
+      </c>
+      <c r="U3" s="15">
+        <f t="shared" si="0"/>
+        <v>199.59898119848106</v>
+      </c>
+      <c r="V3" s="15">
+        <f t="shared" si="0"/>
+        <v>198.50542743354637</v>
+      </c>
+      <c r="W3" s="15">
+        <f t="shared" si="0"/>
+        <v>197.41187366861166</v>
+      </c>
+      <c r="X3" s="15">
+        <f t="shared" si="0"/>
+        <v>196.31831990367695</v>
+      </c>
+      <c r="Y3" s="15">
+        <f t="shared" si="0"/>
+        <v>195.22476613874224</v>
+      </c>
+      <c r="Z3" s="15">
+        <f t="shared" si="0"/>
+        <v>194.13121237380756</v>
+      </c>
+      <c r="AA3" s="15">
+        <f t="shared" si="0"/>
+        <v>193.03765860887285</v>
+      </c>
+      <c r="AB3" s="15">
+        <f t="shared" si="0"/>
+        <v>191.94410484393813</v>
+      </c>
+      <c r="AC3" s="15">
+        <f t="shared" si="0"/>
+        <v>190.85055107900342</v>
+      </c>
+      <c r="AD3" s="15">
+        <f t="shared" si="0"/>
+        <v>189.75699731406874</v>
+      </c>
+      <c r="AE3" s="15">
+        <f t="shared" si="0"/>
+        <v>188.66344354913403</v>
+      </c>
+      <c r="AF3" s="15">
+        <f t="shared" si="0"/>
+        <v>187.56988978419932</v>
+      </c>
+      <c r="AG3" s="15">
+        <f t="shared" si="0"/>
+        <v>186.47633601926464</v>
+      </c>
+      <c r="AH3" s="15">
+        <f t="shared" si="0"/>
+        <v>185.38278225432992</v>
+      </c>
+      <c r="AI3" s="15">
+        <f t="shared" si="0"/>
+        <v>184.28922848939521</v>
+      </c>
+      <c r="AJ3" s="15">
+        <f t="shared" si="0"/>
+        <v>183.1956747244605</v>
+      </c>
+      <c r="AK3" s="15">
+        <f t="shared" si="0"/>
+        <v>182.10212095952579</v>
+      </c>
+      <c r="AL3" s="15">
+        <f t="shared" si="0"/>
+        <v>181.00856719459111</v>
+      </c>
+      <c r="AM3" s="15">
+        <f t="shared" si="0"/>
+        <v>179.9150134296564</v>
+      </c>
+      <c r="AN3" s="15">
+        <f t="shared" si="0"/>
+        <v>178.82145966472169</v>
+      </c>
+      <c r="AO3" s="15">
+        <f t="shared" si="0"/>
+        <v>177.727905899787</v>
+      </c>
+      <c r="AP3" s="15">
+        <f t="shared" si="0"/>
+        <v>176.63435213485229</v>
+      </c>
+      <c r="AQ3" s="15">
+        <f t="shared" si="0"/>
+        <v>175.54079836991758</v>
+      </c>
+      <c r="AR3" s="15">
+        <f t="shared" si="0"/>
+        <v>174.44724460498287</v>
+      </c>
+      <c r="AS3" s="15">
+        <f t="shared" si="0"/>
+        <v>173.35369084004819</v>
+      </c>
+      <c r="AT3" s="15">
+        <f t="shared" si="0"/>
+        <v>172.26013707511348</v>
+      </c>
+      <c r="AU3" s="15">
+        <f t="shared" si="0"/>
+        <v>171.16658331017877</v>
+      </c>
+      <c r="AV3" s="15">
+        <f t="shared" si="0"/>
+        <v>170.07302954524408</v>
+      </c>
+      <c r="AW3" s="15">
+        <f t="shared" si="0"/>
+        <v>168.97947578030937</v>
+      </c>
+      <c r="AX3" s="15">
+        <f t="shared" si="0"/>
+        <v>167.88592201537466</v>
+      </c>
+      <c r="AY3" s="15">
+        <f t="shared" si="0"/>
+        <v>166.79236825043995</v>
+      </c>
+      <c r="AZ3" s="15">
+        <f t="shared" si="0"/>
+        <v>165.69881448550524</v>
+      </c>
+      <c r="BA3" s="15">
+        <f t="shared" si="0"/>
+        <v>164.60526072057056</v>
+      </c>
+      <c r="BB3" s="15">
+        <f t="shared" si="0"/>
+        <v>163.51170695563584</v>
+      </c>
+      <c r="BC3" s="15">
+        <f t="shared" si="0"/>
+        <v>162.41815319070113</v>
+      </c>
+      <c r="BD3" s="15">
+        <f t="shared" si="0"/>
+        <v>161.32459942576645</v>
+      </c>
+      <c r="BE3" s="15">
+        <f t="shared" si="0"/>
+        <v>160.23104566083174</v>
+      </c>
+      <c r="BF3" s="15">
+        <f t="shared" si="0"/>
+        <v>159.13749189589703</v>
+      </c>
+      <c r="BG3" s="15">
+        <f t="shared" si="0"/>
+        <v>158.04393813096232</v>
+      </c>
+      <c r="BH3" s="15">
+        <f t="shared" si="0"/>
+        <v>156.95038436602761</v>
+      </c>
+      <c r="BI3" s="15">
+        <f t="shared" si="0"/>
+        <v>155.85683060109292</v>
+      </c>
+      <c r="BJ3" s="12">
+        <f t="shared" si="0"/>
+        <v>154.76327683615821</v>
+      </c>
+      <c r="BK3" s="12">
+        <f>$Q$9+BK1*$Q$10</f>
+        <v>153.66972307122353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="15">
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1.440766184599692</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="K4" s="15">
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="L4" s="15">
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="N4" s="15">
+        <f>B4</f>
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="O4" s="15">
+        <f>C4</f>
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="P4" s="15">
+        <f>D4</f>
+        <v>1.440766184599692</v>
+      </c>
+      <c r="Q4" s="15">
+        <f t="shared" ref="Q4:BJ4" si="1">E4</f>
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="R4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="S4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="T4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="V4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="W4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="AA4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="AB4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.440766184599692</v>
+      </c>
+      <c r="AC4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="AD4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="AE4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="AF4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="AG4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="AH4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="AI4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="AJ4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="AK4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="AL4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="AM4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="AN4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.440766184599692</v>
+      </c>
+      <c r="AO4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="AP4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="AQ4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="AR4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="AS4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="AT4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="AU4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="AV4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="AW4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="AX4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="AY4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="AZ4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.440766184599692</v>
+      </c>
+      <c r="BA4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="BB4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="BC4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="BD4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="BE4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="BF4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="BG4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="BH4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="BI4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="BJ4" s="15">
+        <f t="shared" si="1"/>
+        <v>1.3893343891484908</v>
+      </c>
+    </row>
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="15">
+        <f>B3*B4</f>
+        <v>306.17665380617797</v>
+      </c>
+      <c r="C5" s="15">
+        <f t="shared" ref="C5:BJ5" si="2">C3*C4</f>
+        <v>296.7015351223809</v>
+      </c>
+      <c r="D5" s="15">
+        <f t="shared" si="2"/>
+        <v>314.35990244583445</v>
+      </c>
+      <c r="E5" s="15">
+        <f t="shared" si="2"/>
+        <v>175.01083887969997</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" si="2"/>
+        <v>211.161592972557</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="2"/>
+        <v>205.52037119913197</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="2"/>
+        <v>199.27879851012119</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="2"/>
+        <v>200.70331560843596</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="2"/>
+        <v>224.3496858557493</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="2"/>
+        <v>156.70202830597188</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="2"/>
+        <v>120.40334424805414</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="2"/>
+        <v>171.25771733122755</v>
+      </c>
+      <c r="N5" s="15">
+        <f t="shared" si="2"/>
+        <v>287.94491158209888</v>
+      </c>
+      <c r="O5" s="15">
+        <f t="shared" si="2"/>
+        <v>278.94589571732922</v>
+      </c>
+      <c r="P5" s="15">
+        <f t="shared" si="2"/>
+        <v>295.45323901911922</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="2"/>
+        <v>164.43207732476174</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" si="2"/>
+        <v>198.33303134056951</v>
+      </c>
+      <c r="S5" s="15">
+        <f t="shared" si="2"/>
+        <v>192.97099333388874</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="2"/>
+        <v>187.04830597519253</v>
+      </c>
+      <c r="U5" s="15">
+        <f t="shared" si="2"/>
+        <v>188.32207143561533</v>
+      </c>
+      <c r="V5" s="15">
+        <f t="shared" si="2"/>
+        <v>210.43819818208553</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" si="2"/>
+        <v>146.9347695800567</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" si="2"/>
+        <v>112.85940285944889</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" si="2"/>
+        <v>160.47114578457865</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" si="2"/>
+        <v>269.71316935801985</v>
+      </c>
+      <c r="AA5" s="15">
+        <f t="shared" si="2"/>
+        <v>261.19025631227748</v>
+      </c>
+      <c r="AB5" s="15">
+        <f t="shared" si="2"/>
+        <v>276.546575592404</v>
+      </c>
+      <c r="AC5" s="15">
+        <f t="shared" si="2"/>
+        <v>153.85331576982347</v>
+      </c>
+      <c r="AD5" s="15">
+        <f t="shared" si="2"/>
+        <v>185.50446970858195</v>
+      </c>
+      <c r="AE5" s="15">
+        <f t="shared" si="2"/>
+        <v>180.42161546864554</v>
+      </c>
+      <c r="AF5" s="15">
+        <f t="shared" si="2"/>
+        <v>174.81781344026388</v>
+      </c>
+      <c r="AG5" s="15">
+        <f t="shared" si="2"/>
+        <v>175.9408272627947</v>
+      </c>
+      <c r="AH5" s="15">
+        <f t="shared" si="2"/>
+        <v>196.52671050842176</v>
+      </c>
+      <c r="AI5" s="15">
+        <f t="shared" si="2"/>
+        <v>137.16751085414154</v>
+      </c>
+      <c r="AJ5" s="15">
+        <f t="shared" si="2"/>
+        <v>105.31546147084364</v>
+      </c>
+      <c r="AK5" s="15">
+        <f t="shared" si="2"/>
+        <v>149.68457423792975</v>
+      </c>
+      <c r="AL5" s="15">
+        <f t="shared" si="2"/>
+        <v>251.4814271339408</v>
+      </c>
+      <c r="AM5" s="15">
+        <f t="shared" si="2"/>
+        <v>243.43461690722583</v>
+      </c>
+      <c r="AN5" s="15">
+        <f t="shared" si="2"/>
+        <v>257.63991216568877</v>
+      </c>
+      <c r="AO5" s="15">
+        <f t="shared" si="2"/>
+        <v>143.27455421488526</v>
+      </c>
+      <c r="AP5" s="15">
+        <f t="shared" si="2"/>
+        <v>172.6759080765944</v>
+      </c>
+      <c r="AQ5" s="15">
+        <f t="shared" si="2"/>
+        <v>167.87223760340231</v>
+      </c>
+      <c r="AR5" s="15">
+        <f t="shared" si="2"/>
+        <v>162.58732090533522</v>
+      </c>
+      <c r="AS5" s="15">
+        <f t="shared" si="2"/>
+        <v>163.55958308997404</v>
+      </c>
+      <c r="AT5" s="15">
+        <f t="shared" si="2"/>
+        <v>182.61522283475799</v>
+      </c>
+      <c r="AU5" s="15">
+        <f t="shared" si="2"/>
+        <v>127.40025212822637</v>
+      </c>
+      <c r="AV5" s="15">
+        <f t="shared" si="2"/>
+        <v>97.771520082238411</v>
+      </c>
+      <c r="AW5" s="15">
+        <f t="shared" si="2"/>
+        <v>138.89800269128091</v>
+      </c>
+      <c r="AX5" s="15">
+        <f t="shared" si="2"/>
+        <v>233.24968490986171</v>
+      </c>
+      <c r="AY5" s="15">
+        <f t="shared" si="2"/>
+        <v>225.67897750217415</v>
+      </c>
+      <c r="AZ5" s="15">
+        <f t="shared" si="2"/>
+        <v>238.73324873897354</v>
+      </c>
+      <c r="BA5" s="15">
+        <f t="shared" si="2"/>
+        <v>132.69579265994699</v>
+      </c>
+      <c r="BB5" s="15">
+        <f t="shared" si="2"/>
+        <v>159.84734644460684</v>
+      </c>
+      <c r="BC5" s="15">
+        <f t="shared" si="2"/>
+        <v>155.32285973815911</v>
+      </c>
+      <c r="BD5" s="15">
+        <f t="shared" si="2"/>
+        <v>150.35682837040662</v>
+      </c>
+      <c r="BE5" s="15">
+        <f t="shared" si="2"/>
+        <v>151.17833891715338</v>
+      </c>
+      <c r="BF5" s="15">
+        <f t="shared" si="2"/>
+        <v>168.70373516109419</v>
+      </c>
+      <c r="BG5" s="15">
+        <f t="shared" si="2"/>
+        <v>117.63299340231119</v>
+      </c>
+      <c r="BH5" s="15">
+        <f t="shared" si="2"/>
+        <v>90.227578693633149</v>
+      </c>
+      <c r="BI5" s="15">
+        <f t="shared" si="2"/>
+        <v>128.11143114463201</v>
+      </c>
+      <c r="BJ5" s="15">
+        <f t="shared" si="2"/>
+        <v>215.01794268578266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="AF8" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="11"/>
+    </row>
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="P9" t="s">
         <v>209</v>
       </c>
-      <c r="Q6">
-        <f>INTERCEPT(B2:BJ2,B1:BJ1)</f>
-        <v>1796.8451661602789</v>
+      <c r="Q9">
+        <f>INTERCEPT(B2:BI2,B1:BI1)</f>
+        <v>221.47005649717514</v>
+      </c>
+      <c r="T9" t="s">
+        <v>208</v>
+      </c>
+      <c r="U9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>2021</v>
+      </c>
+      <c r="AG9" s="6">
+        <v>2022</v>
+      </c>
+      <c r="AH9" s="6">
+        <v>2023</v>
+      </c>
+      <c r="AI9" s="6">
+        <v>2024</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="P7" t="s">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="P10" t="s">
         <v>210</v>
       </c>
-      <c r="Q7">
-        <f>SLOPE(B2:BJ2,B1:BJ1)</f>
-        <v>-3.5966666056921809E-2</v>
-      </c>
+      <c r="Q10">
+        <f>SLOPE(B2:BI2,B1:BI1)</f>
+        <v>-1.0935537649347036</v>
+      </c>
+      <c r="T10" s="14">
+        <v>43831</v>
+      </c>
+      <c r="U10" s="4">
+        <v>268</v>
+      </c>
+      <c r="V10" s="14">
+        <v>44197</v>
+      </c>
+      <c r="W10" s="4">
+        <v>243</v>
+      </c>
+      <c r="X10" s="14">
+        <v>44562</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>235</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>44927</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>203</v>
+      </c>
+      <c r="AB10" s="14">
+        <v>45292</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>347</v>
+      </c>
+      <c r="AD10" s="5"/>
+      <c r="AF10" s="7">
+        <f>U10/$U$22</f>
+        <v>1.3147996729354048</v>
+      </c>
+      <c r="AG10" s="7">
+        <f>W10/$W$22</f>
+        <v>1.1489361702127661</v>
+      </c>
+      <c r="AH10" s="7">
+        <f>Y10/$Y$22</f>
+        <v>1.4149523331660812</v>
+      </c>
+      <c r="AI10" s="7">
+        <f>AA10/$AA$22</f>
+        <v>1.1230982019363762</v>
+      </c>
+      <c r="AJ10" s="7">
+        <f>AC10/$AC$22</f>
+        <v>1.9448855674918264</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AVERAGE(AF10:AJ10)</f>
+        <v>1.3893343891484908</v>
+      </c>
+      <c r="AM10" s="12"/>
+    </row>
+    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T11" s="14">
+        <v>43862</v>
+      </c>
+      <c r="U11" s="4">
+        <v>301</v>
+      </c>
+      <c r="V11" s="14">
+        <v>44228</v>
+      </c>
+      <c r="W11" s="4">
+        <v>325</v>
+      </c>
+      <c r="X11" s="14">
+        <v>44593</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>77</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>44958</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>334</v>
+      </c>
+      <c r="AB11" s="14">
+        <v>45323</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>257</v>
+      </c>
+      <c r="AF11" s="7">
+        <f>U11/$U$22</f>
+        <v>1.4766966475878986</v>
+      </c>
+      <c r="AG11" s="7">
+        <f>W11/$W$22</f>
+        <v>1.5366430260047281</v>
+      </c>
+      <c r="AH11" s="7">
+        <f>Y11/$Y$22</f>
+        <v>0.46362267937782237</v>
+      </c>
+      <c r="AI11" s="7">
+        <f>AA11/$AA$22</f>
+        <v>1.8478561549100969</v>
+      </c>
+      <c r="AJ11" s="7">
+        <f t="shared" ref="AJ11:AJ21" si="3">AC11/$AC$22</f>
+        <v>1.4404483886034565</v>
+      </c>
+      <c r="AL11" s="12">
+        <f t="shared" ref="AL11:AM21" si="4">AVERAGE(AF11:AJ11)</f>
+        <v>1.3530533792968005</v>
+      </c>
+      <c r="AM11" s="12"/>
+    </row>
+    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T12" s="14">
+        <v>43891</v>
+      </c>
+      <c r="U12" s="4">
+        <v>268</v>
+      </c>
+      <c r="V12" s="14">
+        <v>44256</v>
+      </c>
+      <c r="W12" s="4">
+        <v>307</v>
+      </c>
+      <c r="X12" s="14">
+        <v>44621</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>318</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>44986</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>224</v>
+      </c>
+      <c r="AB12" s="14">
+        <v>45352</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>229</v>
+      </c>
+      <c r="AF12" s="7">
+        <f>U12/$U$22</f>
+        <v>1.3147996729354048</v>
+      </c>
+      <c r="AG12" s="7">
+        <f>W12/$W$22</f>
+        <v>1.4515366430260048</v>
+      </c>
+      <c r="AH12" s="7">
+        <f>Y12/$Y$22</f>
+        <v>1.9147014550928247</v>
+      </c>
+      <c r="AI12" s="7">
+        <f>AA12/$AA$22</f>
+        <v>1.2392807745504841</v>
+      </c>
+      <c r="AJ12" s="7">
+        <f t="shared" si="3"/>
+        <v>1.2835123773937414</v>
+      </c>
+      <c r="AL12" s="12">
+        <f t="shared" si="4"/>
+        <v>1.440766184599692</v>
+      </c>
+      <c r="AM12" s="12"/>
+    </row>
+    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T13" s="14">
+        <v>43922</v>
+      </c>
+      <c r="U13" s="4">
+        <v>253</v>
+      </c>
+      <c r="V13" s="14">
+        <v>44287</v>
+      </c>
+      <c r="W13" s="4">
+        <v>98</v>
+      </c>
+      <c r="X13" s="14">
+        <v>44652</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>114</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>45017</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>189</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>45383</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>106</v>
+      </c>
+      <c r="AF13" s="7">
+        <f>U13/$U$22</f>
+        <v>1.241210139002453</v>
+      </c>
+      <c r="AG13" s="7">
+        <f>W13/$W$22</f>
+        <v>0.46335697399527187</v>
+      </c>
+      <c r="AH13" s="7">
+        <f>Y13/$Y$22</f>
+        <v>0.68640240842950317</v>
+      </c>
+      <c r="AI13" s="7">
+        <f>AA13/$AA$22</f>
+        <v>1.045643153526971</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" si="3"/>
+        <v>0.5941148995796357</v>
+      </c>
+      <c r="AL13" s="12">
+        <f t="shared" si="4"/>
+        <v>0.80614551490676711</v>
+      </c>
+      <c r="AM13" s="12"/>
+    </row>
+    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T14" s="14">
+        <v>43952</v>
+      </c>
+      <c r="U14" s="4">
+        <v>161</v>
+      </c>
+      <c r="V14" s="14">
+        <v>44317</v>
+      </c>
+      <c r="W14" s="4">
+        <v>172</v>
+      </c>
+      <c r="X14" s="14">
+        <v>44682</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>222</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>45047</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>187</v>
+      </c>
+      <c r="AB14" s="14">
+        <v>45413</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>163</v>
+      </c>
+      <c r="AF14" s="7">
+        <f>U14/$U$22</f>
+        <v>0.78986099754701555</v>
+      </c>
+      <c r="AG14" s="7">
+        <f>W14/$W$22</f>
+        <v>0.81323877068557915</v>
+      </c>
+      <c r="AH14" s="7">
+        <f>Y14/$Y$22</f>
+        <v>1.3366783743100852</v>
+      </c>
+      <c r="AI14" s="7">
+        <f>AA14/$AA$22</f>
+        <v>1.0345781466113417</v>
+      </c>
+      <c r="AJ14" s="7">
+        <f t="shared" si="3"/>
+        <v>0.91359177954227</v>
+      </c>
+      <c r="AL14" s="12">
+        <f t="shared" si="4"/>
+        <v>0.97758961373925835</v>
+      </c>
+      <c r="AM14" s="12"/>
+    </row>
+    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T15" s="14">
+        <v>43983</v>
+      </c>
+      <c r="U15" s="4">
+        <v>318</v>
+      </c>
+      <c r="V15" s="14">
+        <v>44348</v>
+      </c>
+      <c r="W15" s="4">
+        <v>108</v>
+      </c>
+      <c r="X15" s="14">
+        <v>44713</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>118</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>45078</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>163</v>
+      </c>
+      <c r="AB15" s="14">
+        <v>45444</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>196</v>
+      </c>
+      <c r="AF15" s="7">
+        <f>U15/$U$22</f>
+        <v>1.5600981193785772</v>
+      </c>
+      <c r="AG15" s="7">
+        <f>W15/$W$22</f>
+        <v>0.51063829787234039</v>
+      </c>
+      <c r="AH15" s="7">
+        <f>Y15/$Y$22</f>
+        <v>0.7104867034621174</v>
+      </c>
+      <c r="AI15" s="7">
+        <f>AA15/$AA$22</f>
+        <v>0.90179806362378978</v>
+      </c>
+      <c r="AJ15" s="7">
+        <f t="shared" si="3"/>
+        <v>1.0985520784680056</v>
+      </c>
+      <c r="AL15" s="12">
+        <f t="shared" si="4"/>
+        <v>0.95631465256096604</v>
+      </c>
+      <c r="AM15" s="12"/>
+    </row>
+    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
+      <c r="T16" s="14">
+        <v>44013</v>
+      </c>
+      <c r="U16" s="4">
+        <v>125</v>
+      </c>
+      <c r="V16" s="14">
+        <v>44378</v>
+      </c>
+      <c r="W16" s="4">
+        <v>390</v>
+      </c>
+      <c r="X16" s="14">
+        <v>44743</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>200</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>45108</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>64</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>45474</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>115</v>
+      </c>
+      <c r="AF16" s="7">
+        <f>U16/$U$22</f>
+        <v>0.61324611610793134</v>
+      </c>
+      <c r="AG16" s="7">
+        <f>W16/$W$22</f>
+        <v>1.8439716312056738</v>
+      </c>
+      <c r="AH16" s="7">
+        <f>Y16/$Y$22</f>
+        <v>1.2042147516307073</v>
+      </c>
+      <c r="AI16" s="7">
+        <f>AA16/$AA$22</f>
+        <v>0.35408022130013833</v>
+      </c>
+      <c r="AJ16" s="7">
+        <f t="shared" si="3"/>
+        <v>0.64455861746847276</v>
+      </c>
+      <c r="AL16" s="12">
+        <f t="shared" si="4"/>
+        <v>0.93201426754258476</v>
+      </c>
+      <c r="AM16" s="12"/>
+    </row>
+    <row r="17" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T17" s="14">
+        <v>44044</v>
+      </c>
+      <c r="U17" s="4">
+        <v>87</v>
+      </c>
+      <c r="V17" s="14">
+        <v>44409</v>
+      </c>
+      <c r="W17" s="4">
+        <v>86</v>
+      </c>
+      <c r="X17" s="14">
+        <v>44774</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>209</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>45139</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>274</v>
+      </c>
+      <c r="AB17" s="14">
+        <v>45505</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>198</v>
+      </c>
+      <c r="AF17" s="7">
+        <f>U17/$U$22</f>
+        <v>0.42681929681112019</v>
+      </c>
+      <c r="AG17" s="7">
+        <f>W17/$W$22</f>
+        <v>0.40661938534278957</v>
+      </c>
+      <c r="AH17" s="7">
+        <f>Y17/$Y$22</f>
+        <v>1.2584044154540892</v>
+      </c>
+      <c r="AI17" s="7">
+        <f>AA17/$AA$22</f>
+        <v>1.5159059474412171</v>
+      </c>
+      <c r="AJ17" s="7">
+        <f t="shared" si="3"/>
+        <v>1.109761793554414</v>
+      </c>
+      <c r="AL17" s="12">
+        <f t="shared" si="4"/>
+        <v>0.94350216772072604</v>
+      </c>
+      <c r="AM17" s="12"/>
+    </row>
+    <row r="18" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T18" s="14">
+        <v>44075</v>
+      </c>
+      <c r="U18" s="4">
+        <v>295</v>
+      </c>
+      <c r="V18" s="14">
+        <v>44440</v>
+      </c>
+      <c r="W18" s="4">
+        <v>293</v>
+      </c>
+      <c r="X18" s="14">
+        <v>44805</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>115</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>45170</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>249</v>
+      </c>
+      <c r="AB18" s="14">
+        <v>45536</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>71</v>
+      </c>
+      <c r="AF18" s="7">
+        <f>U18/$U$22</f>
+        <v>1.4472608340147179</v>
+      </c>
+      <c r="AG18" s="7">
+        <f>W18/$W$22</f>
+        <v>1.3853427895981087</v>
+      </c>
+      <c r="AH18" s="7">
+        <f>Y18/$Y$22</f>
+        <v>0.69242348218765681</v>
+      </c>
+      <c r="AI18" s="7">
+        <f>AA18/$AA$22</f>
+        <v>1.3775933609958506</v>
+      </c>
+      <c r="AJ18" s="7">
+        <f t="shared" si="3"/>
+        <v>0.39794488556749186</v>
+      </c>
+      <c r="AL18" s="12">
+        <f t="shared" si="4"/>
+        <v>1.0601130704727653</v>
+      </c>
+      <c r="AM18" s="12"/>
+    </row>
+    <row r="19" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T19" s="14">
+        <v>44105</v>
+      </c>
+      <c r="U19" s="4">
+        <v>79</v>
+      </c>
+      <c r="V19" s="14">
+        <v>44470</v>
+      </c>
+      <c r="W19" s="4">
+        <v>187</v>
+      </c>
+      <c r="X19" s="14">
+        <v>44835</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>159</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>45200</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>56</v>
+      </c>
+      <c r="AB19" s="14">
+        <v>45566</v>
+      </c>
+      <c r="AC19" s="4">
+        <v>211</v>
+      </c>
+      <c r="AF19" s="7">
+        <f>U19/$U$22</f>
+        <v>0.3875715453802126</v>
+      </c>
+      <c r="AG19" s="7">
+        <f>W19/$W$22</f>
+        <v>0.88416075650118209</v>
+      </c>
+      <c r="AH19" s="7">
+        <f>Y19/$Y$22</f>
+        <v>0.95735072754641237</v>
+      </c>
+      <c r="AI19" s="7">
+        <f>AA19/$AA$22</f>
+        <v>0.30982019363762103</v>
+      </c>
+      <c r="AJ19" s="7">
+        <f t="shared" si="3"/>
+        <v>1.1826249416160672</v>
+      </c>
+      <c r="AL19" s="12">
+        <f t="shared" si="4"/>
+        <v>0.74430563293629903</v>
+      </c>
+      <c r="AM19" s="12"/>
+    </row>
+    <row r="20" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T20" s="14">
+        <v>44136</v>
+      </c>
+      <c r="U20" s="4">
+        <v>64</v>
+      </c>
+      <c r="V20" s="14">
+        <v>44501</v>
+      </c>
+      <c r="W20" s="4">
+        <v>85</v>
+      </c>
+      <c r="X20" s="14">
+        <v>44866</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>120</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>45231</v>
+      </c>
+      <c r="AA20" s="4">
+        <v>139</v>
+      </c>
+      <c r="AB20" s="14">
+        <v>45597</v>
+      </c>
+      <c r="AC20" s="4">
+        <v>119</v>
+      </c>
+      <c r="AF20" s="7">
+        <f>U20/$U$22</f>
+        <v>0.31398201144726084</v>
+      </c>
+      <c r="AG20" s="7">
+        <f>W20/$W$22</f>
+        <v>0.40189125295508277</v>
+      </c>
+      <c r="AH20" s="7">
+        <f>Y20/$Y$22</f>
+        <v>0.72252885097842445</v>
+      </c>
+      <c r="AI20" s="7">
+        <f>AA20/$AA$22</f>
+        <v>0.76901798063623794</v>
+      </c>
+      <c r="AJ20" s="7">
+        <f t="shared" si="3"/>
+        <v>0.66697804764128921</v>
+      </c>
+      <c r="AL20" s="12">
+        <f t="shared" si="4"/>
+        <v>0.5748796287316591</v>
+      </c>
+      <c r="AM20" s="12"/>
+    </row>
+    <row r="21" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T21" s="14">
+        <v>44166</v>
+      </c>
+      <c r="U21" s="4">
+        <v>227</v>
+      </c>
+      <c r="V21" s="14">
+        <v>44531</v>
+      </c>
+      <c r="W21" s="4">
+        <v>244</v>
+      </c>
+      <c r="X21" s="14">
+        <v>44896</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z21" s="14">
+        <v>45261</v>
+      </c>
+      <c r="AA21" s="4">
+        <v>87</v>
+      </c>
+      <c r="AB21" s="14">
+        <v>45627</v>
+      </c>
+      <c r="AC21" s="4">
+        <v>129</v>
+      </c>
+      <c r="AF21" s="7">
+        <f>U21/$U$22</f>
+        <v>1.1136549468520032</v>
+      </c>
+      <c r="AG21" s="7">
+        <f>W21/$W$22</f>
+        <v>1.1536643026004729</v>
+      </c>
+      <c r="AH21" s="7">
+        <f>Y21/$Y$22</f>
+        <v>0.63823381836427495</v>
+      </c>
+      <c r="AI21" s="7">
+        <f>AA21/$AA$22</f>
+        <v>0.48132780082987553</v>
+      </c>
+      <c r="AJ21" s="7">
+        <f t="shared" si="3"/>
+        <v>0.72302662307333021</v>
+      </c>
+      <c r="AL21" s="12">
+        <f t="shared" si="4"/>
+        <v>0.82198149834399137</v>
+      </c>
+      <c r="AM21" s="12"/>
+    </row>
+    <row r="22" spans="20:39" x14ac:dyDescent="0.3">
+      <c r="T22" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="U22" s="10">
+        <f>AVERAGE(U10:U21)</f>
+        <v>203.83333333333334</v>
+      </c>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10">
+        <f>AVERAGE(W10:W21)</f>
+        <v>211.5</v>
+      </c>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10">
+        <f>AVERAGE(Y10:Y21)</f>
+        <v>166.08333333333334</v>
+      </c>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10">
+        <f>AVERAGE(AA10:AA21)</f>
+        <v>180.75</v>
+      </c>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10">
+        <f>AVERAGE(AC10:AC21)</f>
+        <v>178.41666666666666</v>
+      </c>
+      <c r="AD22" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="AF8:AJ8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/SALE TRABAJO LARGO.xlsx
+++ b/SALE TRABAJO LARGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\TRABAJO FINAL MATERIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500A9FAF-9DE2-4125-8254-C6DA94720AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697D637-BD00-4E79-9FD1-27903BBA40C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0FCE4E4-E062-49E2-A859-ABF82E26F938}"/>
   </bookViews>
